--- a/award_forms/038_teamwork_excellence_award_nomination_form--award_forms.xlsx
+++ b/award_forms/038_teamwork_excellence_award_nomination_form--award_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nominator_name</t>
+          <t>Nominator Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nominator_email</t>
+          <t>Nominator Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nominator_phone</t>
+          <t>Nominator Phone</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nominee_name</t>
+          <t>Nominee Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nominee_title</t>
+          <t>Nominee Title</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nominee_department</t>
+          <t>Nominee Department</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nominator_name</t>
+          <t>nominator_supervisor_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nominator_name</t>
+          <t>Nominator Supervisor Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nominator_title</t>
+          <t>nominator_supervisor_title</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nominator_title</t>
+          <t>Nominator Supervisor Title</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nominator_email</t>
+          <t>nominator_supervisor_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nominator_email</t>
+          <t>Nominator Supervisor Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nominator_phone</t>
+          <t>nominator_supervisor_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nominator_phone</t>
+          <t>Nominator Supervisor Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nominator_supervisor_name</t>
+          <t>nominator_supervisor_organizational_impact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nominator_supervisor_name</t>
+          <t>Nominee's Supervisor's Organizational Impact</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nominator_supervisor_title</t>
+          <t>nominator_supervisor_direct_manager</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nominator_supervisor_title</t>
+          <t>Nominee's Supervisor's Direct Manager</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nominator_supervisor_email</t>
+          <t>nominator_supervisor_indirect_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nominator_supervisor_email</t>
+          <t>Nominee's Supervisor's Indirect Manager</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nominator_supervisor_phone</t>
+          <t>nominator_supervisor_employees</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nominator_supervisor_phone</t>
+          <t>Nominee's Supervisor's Number of Employees</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nominator_supervisor_department</t>
+          <t>nominator_supervisor_employees_count</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nominator_supervisor_department</t>
+          <t>Nominator Supervisor Employees Count</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nominator_supervisor_job_title</t>
+          <t>nominator_organizational_impact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nominator_supervisor_job_title</t>
+          <t>Nominee's Organizational Impact</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nominator_supervisor_direct_manager</t>
+          <t>nominator_collaboration</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nominator_supervisor_direct_manager</t>
+          <t>Nominee's Collaboration</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nominator_supervisor_indirect_manager</t>
+          <t>nominator_leadership_skills</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nominator_supervisor_indirect_manager</t>
+          <t>Nominee's Leadership Skills</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nominator_supervisor_employees</t>
+          <t>nominator_achievement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nominator_supervisor_employees</t>
+          <t>Nominee's Achievement</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nominator_supervisor_employees_count</t>
+          <t>nominator_additional_comments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nominator_supervisor_employees_count</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nominator_organizational_impact</t>
+          <t>nominator_departmental_contribution</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nominator_organizational_impact</t>
+          <t>Nominee's Departmental Contribution</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nominator_collaboration</t>
+          <t>nominator_supervisor_departmental_contribution</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nominator_collaboration</t>
+          <t>Nominee's Supervisor's Departmental Contribution</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nominator_leadership_skills</t>
+          <t>nominator_supervisor_departmental_contribution_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nominator_leadership_skills</t>
+          <t>Nominator Supervisor Departmental Contribution 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nominator_achievement</t>
+          <t>nominator_supervisor_supervisor_departmental_contribution</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nominator_achievement</t>
+          <t>Nominator Supervisor Supervisor Departmental Contribution</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,16 +1072,200 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nominator_additional_comments</t>
+          <t>nominator_supervisor_organizational_impact_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nominator_additional_comments</t>
+          <t>Nominator Supervisor Organizational Impact 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_job_title</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Nominee's Supervisor's Job Title</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_direct_manager_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nominator Supervisor Direct Manager 2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_indirect_manager_2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nominator Supervisor Indirect Manager 2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_employees_2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Nominator Supervisor Employees 2</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_employees_count_2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Nominator Supervisor Employees Count 2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_leadership_skills</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Nominee's Supervisor's Leadership Skills</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_achievement</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nominee's Supervisor's Achievement</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_additional_comments</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nominee's Supervisor's Additional Comments</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +1282,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1186,6 +1370,74 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_indirect_manager_2_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_indirect_manager_2_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_employees_2_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>nominator_supervisor_employees_2_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
